--- a/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0003T0006Z000C1N26_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0003T0006Z000C1N26_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>30.10492310917195</v>
+        <v>4.892050005240442</v>
       </c>
       <c r="D2" t="n">
-        <v>29.59968978406118</v>
+        <v>4.809949589909941</v>
       </c>
       <c r="E2" t="n">
-        <v>10.09844722806094</v>
+        <v>1.640997674559902</v>
       </c>
       <c r="F2" t="n">
-        <v>10.01119040138682</v>
+        <v>1.626818440225358</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.82718979369964</v>
+        <v>5.659418341476192</v>
       </c>
       <c r="D3" t="n">
-        <v>35.28101249578896</v>
+        <v>5.733164530565707</v>
       </c>
       <c r="E3" t="n">
-        <v>10.09844722806094</v>
+        <v>1.640997674559902</v>
       </c>
       <c r="F3" t="n">
-        <v>10.01119040138682</v>
+        <v>1.626818440225358</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.56371679412739</v>
+        <v>4.966603979045701</v>
       </c>
       <c r="D4" t="n">
-        <v>30.40428225825826</v>
+        <v>4.940695866966966</v>
       </c>
       <c r="E4" t="n">
-        <v>10.09844722806094</v>
+        <v>1.640997674559902</v>
       </c>
       <c r="F4" t="n">
-        <v>10.01119040138682</v>
+        <v>1.626818440225358</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>8.901554460981824</v>
+        <v>1.446502599909546</v>
       </c>
       <c r="D5" t="n">
-        <v>9.193444880359378</v>
+        <v>1.493934793058399</v>
       </c>
       <c r="E5" t="n">
-        <v>10.09844722806094</v>
+        <v>1.640997674559902</v>
       </c>
       <c r="F5" t="n">
-        <v>10.01119040138682</v>
+        <v>1.626818440225358</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
